--- a/04_Figures/F06_prediction/modules/T3/ridge/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/T3/ridge/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -171,12 +171,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -569,16 +563,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0662197923895917</v>
+        <v>-0.112354637327623</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.610714285714286</v>
+        <v>-0.560714285714286</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -602,28 +596,28 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0662197923895917</v>
+        <v>-0.112354637327623</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.610714285714286</v>
+        <v>-0.560714285714286</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0298507462686567</v>
+        <v>0.0398009950248756</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0646766169154229</v>
+        <v>0.0497512437810945</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.196791599439833</v>
+        <v>-0.235007281133059</v>
       </c>
       <c r="M3" t="n">
-        <v>0.212479431227124</v>
+        <v>0.604799103620348</v>
       </c>
     </row>
     <row r="4">
@@ -643,13 +637,13 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.158809271467948</v>
       </c>
       <c r="I4" t="n">
         <v>-1</v>
@@ -676,28 +670,28 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.158809271467948</v>
       </c>
       <c r="I5" t="n">
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.313432835820896</v>
+        <v>0.781094527363184</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.237909274599874</v>
+        <v>-0.172950713636933</v>
       </c>
       <c r="M5" t="n">
-        <v>0.471924043530509</v>
+        <v>0.0966560711615916</v>
       </c>
     </row>
     <row r="6">
@@ -717,7 +711,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -750,7 +744,7 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
@@ -762,16 +756,16 @@
         <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.621890547263682</v>
+        <v>0.661691542288557</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.22900225136431</v>
+        <v>-0.168104764518577</v>
       </c>
       <c r="M7" t="n">
-        <v>0.529454410584484</v>
+        <v>0.0786518297166295</v>
       </c>
     </row>
     <row r="8">
@@ -791,16 +785,16 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.158867853247046</v>
+        <v>-0.146696301365116</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.860714285714286</v>
+        <v>-0.792857142857143</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -824,28 +818,28 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.158867853247046</v>
+        <v>-0.146696301365116</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.860714285714286</v>
+        <v>-0.792857142857143</v>
       </c>
       <c r="J9" t="n">
-        <v>0.701492537313433</v>
+        <v>0.0597014925373134</v>
       </c>
       <c r="K9" t="n">
-        <v>0.134328358208955</v>
+        <v>0.0746268656716418</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.191054918862354</v>
+        <v>-0.202576715924291</v>
       </c>
       <c r="M9" t="n">
-        <v>0.152213662410843</v>
+        <v>0.259668499580533</v>
       </c>
     </row>
     <row r="10">
@@ -865,7 +859,7 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -898,7 +892,7 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
@@ -910,16 +904,16 @@
         <v>-0.996415759077198</v>
       </c>
       <c r="J11" t="n">
-        <v>0.213930348258706</v>
+        <v>0.243781094527363</v>
       </c>
       <c r="K11" t="n">
-        <v>0.482587064676617</v>
+        <v>0.45771144278607</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.183617528385355</v>
+        <v>-0.179400298241401</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0977292643922199</v>
+        <v>0.132722717706273</v>
       </c>
     </row>
     <row r="12">
@@ -939,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -972,7 +966,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
@@ -984,16 +978,16 @@
         <v>-1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.582089552238806</v>
+        <v>0.45771144278607</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.159593872043964</v>
+        <v>-0.213851130363</v>
       </c>
       <c r="M13" t="n">
-        <v>0.00475118062019547</v>
+        <v>0.421354216980252</v>
       </c>
     </row>
   </sheetData>
@@ -1048,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.164082899071945</v>
+        <v>-0.12711942233317</v>
       </c>
     </row>
     <row r="5">
@@ -1059,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.14795918367347</v>
+        <v>-8.09965080138754</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.44941950186415</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="7">
@@ -1092,7 +1086,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.283490904590949</v>
       </c>
     </row>
     <row r="9">
@@ -1147,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.159797854260779</v>
       </c>
     </row>
     <row r="14">
@@ -1180,7 +1174,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.177753483655285</v>
+        <v>-0.15636629715909</v>
       </c>
     </row>
     <row r="17">
@@ -1202,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.28908358069966</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.303600366181606</v>
+        <v>-0.331535333807559</v>
       </c>
     </row>
     <row r="20">
@@ -1224,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.179460426044113</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="21">
@@ -1235,7 +1229,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.81596642068615</v>
       </c>
     </row>
     <row r="22">
@@ -1246,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.176249931047744</v>
+        <v>-0.247960174133617</v>
       </c>
     </row>
     <row r="23">
@@ -1257,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.193278071331149</v>
       </c>
     </row>
     <row r="24">
@@ -1323,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.184899649453212</v>
+        <v>-0.182313614710369</v>
       </c>
     </row>
     <row r="30">
@@ -1356,7 +1350,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.190370231441545</v>
+        <v>-0.34601119228504</v>
       </c>
     </row>
     <row r="33">
@@ -1367,7 +1361,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.153481089640122</v>
       </c>
     </row>
     <row r="34">
@@ -1378,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.284736316317768</v>
+        <v>-0.175432970958765</v>
       </c>
     </row>
     <row r="35">
@@ -1389,7 +1383,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.219343577970871</v>
+        <v>-0.51046176255619</v>
       </c>
     </row>
     <row r="36">
@@ -1411,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.500789401249987</v>
+        <v>0.137416805930517</v>
       </c>
     </row>
     <row r="38">
@@ -1422,7 +1416,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.260422147069412</v>
+        <v>-0.225902746171615</v>
       </c>
     </row>
     <row r="39">
@@ -1433,7 +1427,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.216347005618936</v>
       </c>
     </row>
     <row r="40">
@@ -1488,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.268319630389964</v>
       </c>
     </row>
     <row r="45">
@@ -1510,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.193014006457465</v>
+        <v>-0.198661275608885</v>
       </c>
     </row>
     <row r="47">
@@ -1532,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.530571546508294</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="49">
@@ -1543,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.125063599632055</v>
+        <v>0.0224156830424893</v>
       </c>
     </row>
     <row r="50">
@@ -1565,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.381408015683973</v>
+        <v>-0.26100114918336</v>
       </c>
     </row>
     <row r="52">
@@ -1576,7 +1570,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.198544607701161</v>
+        <v>-0.177541246410795</v>
       </c>
     </row>
     <row r="53">
@@ -1587,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2509187646098</v>
+        <v>0.245320087788321</v>
       </c>
     </row>
     <row r="54">
@@ -1598,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.197518759487956</v>
+        <v>0.187753960883581</v>
       </c>
     </row>
     <row r="55">
@@ -1642,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.815271673602178</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="59">
@@ -1653,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.148259807571536</v>
+        <v>-0.150824784411781</v>
       </c>
     </row>
     <row r="60">
@@ -1686,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.367916878303273</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="63">
@@ -1697,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.404948172745777</v>
       </c>
     </row>
     <row r="64">
@@ -1719,7 +1713,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.182985855239817</v>
+        <v>-0.169134281908547</v>
       </c>
     </row>
     <row r="66">
@@ -1741,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.346786943208485</v>
+        <v>-0.193944440095383</v>
       </c>
     </row>
     <row r="68">
@@ -1785,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.158071152976803</v>
+        <v>-0.176944242905404</v>
       </c>
     </row>
     <row r="72">
@@ -1796,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.80082167305021</v>
       </c>
     </row>
     <row r="73">
@@ -1818,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.174936182121186</v>
+        <v>-0.150717597461531</v>
       </c>
     </row>
     <row r="75">
@@ -1840,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.298600966090186</v>
       </c>
     </row>
     <row r="77">
@@ -1884,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.217701975681123</v>
       </c>
     </row>
     <row r="81">
@@ -1895,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0489006893579823</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="82">
@@ -1950,7 +1944,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.17836933864269</v>
+        <v>-0.187907242069249</v>
       </c>
     </row>
     <row r="87">
@@ -1972,7 +1966,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.235044936022322</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="89">
@@ -1994,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.154373455069688</v>
       </c>
     </row>
     <row r="91">
@@ -2005,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.325670203405213</v>
+        <v>-0.239456773472775</v>
       </c>
     </row>
     <row r="92">
@@ -2016,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.271461983153993</v>
+        <v>-0.240605089257028</v>
       </c>
     </row>
     <row r="93">
@@ -2038,7 +2032,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.0516022702603296</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="95">
@@ -2093,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.290526220451834</v>
+        <v>-0.269941078213792</v>
       </c>
     </row>
     <row r="100">
@@ -2126,7 +2120,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.376315371165432</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="103">
@@ -2137,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.19567796242623</v>
+        <v>-0.406483442045649</v>
       </c>
     </row>
     <row r="104">
@@ -2148,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.2306761715807</v>
+        <v>-0.240545759850603</v>
       </c>
     </row>
     <row r="105">
@@ -2181,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.06838595538935</v>
       </c>
     </row>
     <row r="108">
@@ -2225,7 +2219,7 @@
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.179831924457193</v>
       </c>
     </row>
     <row r="112">
@@ -2368,7 +2362,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.288836499760462</v>
       </c>
     </row>
     <row r="125">
@@ -2379,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.196011744266764</v>
+        <v>-0.236739451526701</v>
       </c>
     </row>
     <row r="126">
@@ -2390,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.360905728100314</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="127">
@@ -2401,7 +2395,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.209759122342948</v>
+        <v>-0.232933112936916</v>
       </c>
     </row>
     <row r="128">
@@ -2412,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.155731722230561</v>
       </c>
     </row>
     <row r="129">
@@ -2445,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.263080712883632</v>
+        <v>-0.32822618456902</v>
       </c>
     </row>
     <row r="132">
@@ -2456,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.297023198407413</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="133">
@@ -2511,7 +2505,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.197485034392499</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="138">
@@ -2533,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.256235621686909</v>
+        <v>-0.22706005861941</v>
       </c>
     </row>
     <row r="140">
@@ -2544,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.160082908508651</v>
       </c>
     </row>
     <row r="141">
@@ -2555,7 +2549,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.184645815830946</v>
+        <v>-0.202010918450418</v>
       </c>
     </row>
     <row r="142">
@@ -2566,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.289890333863624</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="143">
@@ -2577,7 +2571,7 @@
         <v>16</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.266883347323974</v>
+        <v>0.236139570334237</v>
       </c>
     </row>
     <row r="144">
@@ -2610,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.155274737471507</v>
+        <v>-0.162695106303044</v>
       </c>
     </row>
     <row r="147">
@@ -2654,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.19712811849711</v>
+        <v>-0.171941148395223</v>
       </c>
     </row>
     <row r="151">
@@ -2665,7 +2659,7 @@
         <v>16</v>
       </c>
       <c r="C151" t="n">
-        <v>-1.4420723847573</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="152">
@@ -2687,7 +2681,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.198181015928437</v>
       </c>
     </row>
     <row r="154">
@@ -2698,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.212590556294678</v>
       </c>
     </row>
     <row r="155">
@@ -2709,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.182306046588719</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="156">
@@ -2753,7 +2747,7 @@
         <v>16</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.141220717729235</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="160">
@@ -2775,7 +2769,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.157726893650342</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="162">
@@ -2797,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.152186667348803</v>
+        <v>-1.79441780437942</v>
       </c>
     </row>
     <row r="164">
@@ -2808,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.15194456755571</v>
       </c>
     </row>
     <row r="165">
@@ -2819,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.159640066152113</v>
+        <v>-0.166081157175137</v>
       </c>
     </row>
     <row r="166">
@@ -2841,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.205511321973976</v>
+        <v>-0.162861652821966</v>
       </c>
     </row>
     <row r="168">
@@ -2874,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.152135067859673</v>
+        <v>-0.141302664092605</v>
       </c>
     </row>
     <row r="171">
@@ -2896,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.150526992494867</v>
+        <v>-0.167877397772444</v>
       </c>
     </row>
     <row r="173">
@@ -2929,7 +2923,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.379992046644167</v>
+        <v>-0.352306921395173</v>
       </c>
     </row>
     <row r="176">
@@ -2940,7 +2934,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.129367554208714</v>
+        <v>-0.165716634391355</v>
       </c>
     </row>
     <row r="177">
@@ -2951,7 +2945,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.170487898758754</v>
+        <v>-0.185546551668438</v>
       </c>
     </row>
     <row r="178">
@@ -2984,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.167971438150919</v>
+        <v>-0.194356534841003</v>
       </c>
     </row>
     <row r="181">
@@ -2995,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>0.00403481922462257</v>
+        <v>0.167687945754832</v>
       </c>
     </row>
     <row r="182">
@@ -3006,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.16371285330639</v>
+        <v>-0.157379856038619</v>
       </c>
     </row>
     <row r="183">
@@ -3017,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.153731345147998</v>
+        <v>-0.128146467670321</v>
       </c>
     </row>
     <row r="184">
@@ -3039,7 +3033,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.183453795228079</v>
       </c>
     </row>
     <row r="186">
@@ -3050,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.357810233313519</v>
       </c>
     </row>
     <row r="187">
@@ -3061,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.239501018445738</v>
       </c>
     </row>
     <row r="188">
@@ -3072,7 +3066,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.393310270748215</v>
+        <v>-0.40273112210264</v>
       </c>
     </row>
     <row r="189">
@@ -3083,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.165008647955473</v>
+        <v>-0.167695355202125</v>
       </c>
     </row>
     <row r="190">
@@ -3105,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.247417533753418</v>
+        <v>-0.292208996169696</v>
       </c>
     </row>
     <row r="192">
@@ -3116,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.198738737714094</v>
+        <v>-0.230793341883843</v>
       </c>
     </row>
     <row r="193">
@@ -3160,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.522752539560521</v>
+        <v>-0.915077238903377</v>
       </c>
     </row>
     <row r="197">
@@ -3171,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.24682220748137</v>
+        <v>0.0168351234650596</v>
       </c>
     </row>
     <row r="198">
@@ -3215,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>-1.81210970873197</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="202">
@@ -3237,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-5.98071287731515</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="204">
@@ -3248,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.255757604256299</v>
+        <v>-0.284845267547617</v>
       </c>
     </row>
     <row r="205">
@@ -3270,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.300212947949692</v>
+        <v>-0.135853301516209</v>
       </c>
     </row>
     <row r="207">
@@ -3292,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.995787129607487</v>
+        <v>-0.399085369133802</v>
       </c>
     </row>
     <row r="209">
@@ -3347,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.170522502331742</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="214">
@@ -3369,7 +3363,7 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.149233966762919</v>
       </c>
     </row>
     <row r="216">
@@ -3402,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>0.0481881785434367</v>
+        <v>-0.143573473877454</v>
       </c>
     </row>
     <row r="219">
@@ -3413,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.27825703593284</v>
+        <v>-0.236790845600336</v>
       </c>
     </row>
     <row r="220">
@@ -3424,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.220156761256116</v>
+        <v>-0.177048202277443</v>
       </c>
     </row>
     <row r="221">
@@ -3446,7 +3440,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.186592346052095</v>
+        <v>-0.192167877945609</v>
       </c>
     </row>
     <row r="223">
@@ -3457,7 +3451,7 @@
         <v>16</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.314580938035037</v>
+        <v>-0.375794583080659</v>
       </c>
     </row>
     <row r="224">
@@ -3468,7 +3462,7 @@
         <v>16</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.279855456012777</v>
+        <v>-0.178856386985025</v>
       </c>
     </row>
     <row r="225">
@@ -3556,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.31407831689971</v>
       </c>
     </row>
     <row r="233">
@@ -3567,7 +3561,7 @@
         <v>16</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.152187282931234</v>
       </c>
     </row>
     <row r="234">
@@ -3589,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.191977617639811</v>
+        <v>-0.428925899450065</v>
       </c>
     </row>
     <row r="236">
@@ -3611,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>0.165434322212945</v>
+        <v>0.260789252904689</v>
       </c>
     </row>
     <row r="238">
@@ -3622,7 +3616,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.21544079966206</v>
+        <v>-0.215178212908069</v>
       </c>
     </row>
     <row r="239">
@@ -3677,7 +3671,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.178840593649183</v>
       </c>
     </row>
     <row r="244">
@@ -3688,7 +3682,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.162058271020179</v>
+        <v>-0.193122115832415</v>
       </c>
     </row>
     <row r="245">
@@ -3743,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.130708620509351</v>
+        <v>-0.141723144856646</v>
       </c>
     </row>
     <row r="250">
@@ -3754,7 +3748,7 @@
         <v>16</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.173404660914345</v>
+        <v>-0.168381698094797</v>
       </c>
     </row>
     <row r="251">
@@ -3765,7 +3759,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.379441549005013</v>
+        <v>-0.373985703137742</v>
       </c>
     </row>
     <row r="252">
@@ -3776,7 +3770,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.148540530268553</v>
       </c>
     </row>
     <row r="253">
@@ -3787,7 +3781,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>0.208015887215864</v>
+        <v>0.180621136174235</v>
       </c>
     </row>
     <row r="254">
@@ -3820,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.397266865114586</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="257">
@@ -3919,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.173769332999744</v>
+        <v>-0.157783989903856</v>
       </c>
     </row>
     <row r="266">
@@ -3930,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-1.28980253243633</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="267">
@@ -3941,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.24861129731364</v>
+        <v>-0.515513245399829</v>
       </c>
     </row>
     <row r="268">
@@ -3996,7 +3990,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.222057832565222</v>
+        <v>-0.183597814013254</v>
       </c>
     </row>
     <row r="273">
@@ -4018,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.170049892487446</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="275">
@@ -4029,7 +4023,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-1.08431124356327</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="276">
@@ -4040,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.230620972602437</v>
+        <v>-0.289090021155473</v>
       </c>
     </row>
     <row r="277">
@@ -4095,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.0508579834916003</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="282">
@@ -4139,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.28439320066948</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="286">
@@ -4150,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.144454504865575</v>
+        <v>-0.141684483020007</v>
       </c>
     </row>
     <row r="287">
@@ -4161,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.158208200579908</v>
       </c>
     </row>
     <row r="288">
@@ -4172,7 +4166,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.178955593665426</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="289">
@@ -4194,7 +4188,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.199871263091582</v>
+        <v>-0.152031040049521</v>
       </c>
     </row>
     <row r="291">
@@ -4205,7 +4199,7 @@
         <v>16</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.209795049100032</v>
       </c>
     </row>
     <row r="292">
@@ -4216,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.148420778405533</v>
       </c>
     </row>
     <row r="293">
@@ -4238,7 +4232,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.154150719239001</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="295">
@@ -4249,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.178972267373234</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="296">
@@ -4293,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.440275045719743</v>
+        <v>-0.244464028554273</v>
       </c>
     </row>
     <row r="300">
@@ -4348,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.168067385217321</v>
+        <v>-0.215290919487745</v>
       </c>
     </row>
     <row r="305">
@@ -4403,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.477150239782753</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="310">
@@ -4447,7 +4441,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.370367968589741</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="314">
@@ -4579,7 +4573,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.284492521272735</v>
       </c>
     </row>
     <row r="326">
@@ -4601,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.185249666678621</v>
+        <v>-0.20852912423573</v>
       </c>
     </row>
     <row r="328">
@@ -4612,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.201532196364607</v>
+        <v>-0.363484400705369</v>
       </c>
     </row>
     <row r="329">
@@ -4645,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.10530233747049</v>
+        <v>-0.137005845028981</v>
       </c>
     </row>
     <row r="332">
@@ -4656,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.837866960959635</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="333">
@@ -4678,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.478871593281211</v>
       </c>
     </row>
     <row r="335">
@@ -4722,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.18428197069712</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="339">
@@ -4733,7 +4727,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.232978625846128</v>
       </c>
     </row>
     <row r="340">
@@ -4744,7 +4738,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.175510886949544</v>
+        <v>-0.175712384647415</v>
       </c>
     </row>
     <row r="341">
@@ -4777,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.901705523307677</v>
+        <v>-0.130146659914675</v>
       </c>
     </row>
     <row r="344">
@@ -4810,7 +4804,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.164372473327022</v>
       </c>
     </row>
     <row r="347">
@@ -4821,7 +4815,7 @@
         <v>16</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.217987583752862</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="348">
@@ -4832,7 +4826,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.159691114619654</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="349">
@@ -4876,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.361667136601486</v>
+        <v>-0.433960766206825</v>
       </c>
     </row>
     <row r="353">
@@ -4898,7 +4892,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.161735451792312</v>
       </c>
     </row>
     <row r="355">
@@ -4909,7 +4903,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.148519818786165</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="356">
@@ -4920,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.713414885395831</v>
+        <v>-0.708086942086596</v>
       </c>
     </row>
     <row r="357">
@@ -4931,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.161147600979185</v>
       </c>
     </row>
     <row r="358">
@@ -4953,7 +4947,7 @@
         <v>16</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.198948028704488</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="360">
@@ -4964,7 +4958,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.41324064878344</v>
+        <v>-0.890159437469563</v>
       </c>
     </row>
     <row r="361">
@@ -5041,7 +5035,7 @@
         <v>16</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.061010752207606</v>
+        <v>-0.185749790934136</v>
       </c>
     </row>
     <row r="368">
@@ -5074,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.169961528709682</v>
+        <v>-0.318975646726781</v>
       </c>
     </row>
     <row r="371">
@@ -5096,7 +5090,7 @@
         <v>16</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.155675335135905</v>
+        <v>-0.15622802990221</v>
       </c>
     </row>
     <row r="373">
@@ -5129,7 +5123,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.176347726557079</v>
+        <v>-0.165832817147129</v>
       </c>
     </row>
     <row r="376">
@@ -5184,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.299951723071341</v>
+        <v>-0.228213873471473</v>
       </c>
     </row>
     <row r="381">
@@ -5195,7 +5189,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.156845829702216</v>
+        <v>-0.159825476996674</v>
       </c>
     </row>
     <row r="382">
@@ -5206,7 +5200,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.177761609248376</v>
+        <v>-0.176830309131482</v>
       </c>
     </row>
     <row r="383">
@@ -5217,7 +5211,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.145761475429506</v>
       </c>
     </row>
     <row r="384">
@@ -5239,7 +5233,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.16564198967111</v>
       </c>
     </row>
     <row r="386">
@@ -5250,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.381837276850905</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="387">
@@ -5283,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.152418580798384</v>
       </c>
     </row>
     <row r="390">
@@ -5294,7 +5288,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.218307374390381</v>
+        <v>-0.284277407593005</v>
       </c>
     </row>
     <row r="391">
@@ -5305,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.11397575259865</v>
+        <v>-0.252298997924783</v>
       </c>
     </row>
     <row r="392">
@@ -5316,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.180810673732386</v>
+        <v>-0.214801622010982</v>
       </c>
     </row>
     <row r="393">
@@ -5338,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.766221975430407</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="395">
@@ -5360,7 +5354,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-1.72547255217574</v>
+        <v>-0.196998004418953</v>
       </c>
     </row>
     <row r="397">
@@ -5371,7 +5365,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.26938666501635</v>
       </c>
     </row>
     <row r="398">
@@ -5415,7 +5409,7 @@
         <v>16</v>
       </c>
       <c r="C401" t="n">
-        <v>-2.0883905685317</v>
+        <v>-0.153128096808668</v>
       </c>
     </row>
     <row r="402">
@@ -5437,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="C403" t="n">
-        <v>-6.78695263500963</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="404">
@@ -5448,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.191212023642196</v>
+        <v>-0.251570465968208</v>
       </c>
     </row>
     <row r="405">
@@ -5470,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.14434779298217</v>
+        <v>-0.138086252757325</v>
       </c>
     </row>
     <row r="407">
@@ -5492,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>-0.482145227274465</v>
+        <v>-0.142026669328833</v>
       </c>
     </row>
     <row r="409">
@@ -5536,7 +5530,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.183557287016754</v>
+        <v>-0.153483669471563</v>
       </c>
     </row>
     <row r="413">
@@ -5591,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.221555219172209</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="418">
@@ -5602,7 +5596,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.386183408043737</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="419">
@@ -5624,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>0.149639696544698</v>
+        <v>-0.163234862858828</v>
       </c>
     </row>
     <row r="421">
@@ -5646,7 +5640,7 @@
         <v>16</v>
       </c>
       <c r="C422" t="n">
-        <v>-0.179472567457472</v>
+        <v>-0.195743311264485</v>
       </c>
     </row>
     <row r="423">
@@ -5657,7 +5651,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.370252020530733</v>
+        <v>-0.613859442472062</v>
       </c>
     </row>
     <row r="424">
@@ -5668,7 +5662,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.236601568823888</v>
+        <v>-0.230055292596682</v>
       </c>
     </row>
     <row r="425">
@@ -5756,7 +5750,7 @@
         <v>16</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.19402197023603</v>
       </c>
     </row>
     <row r="433">
@@ -5789,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.315468590544043</v>
       </c>
     </row>
     <row r="436">
@@ -5800,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.155028333056891</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="437">
@@ -5811,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>0.173384505059638</v>
+        <v>0.213017632278006</v>
       </c>
     </row>
     <row r="438">
@@ -5822,7 +5816,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.272811964356763</v>
+        <v>-0.283321173676828</v>
       </c>
     </row>
     <row r="439">
@@ -5833,7 +5827,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.16409984272171</v>
+        <v>-0.295709895627297</v>
       </c>
     </row>
     <row r="440">
@@ -5877,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.471556744564116</v>
+        <v>-0.149178606121729</v>
       </c>
     </row>
     <row r="444">
@@ -5888,7 +5882,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.148881222229792</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="445">
@@ -5943,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.148343252248649</v>
+        <v>-0.17668055807716</v>
       </c>
     </row>
     <row r="450">
@@ -5976,7 +5970,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.157760813670922</v>
+        <v>-0.156627679346293</v>
       </c>
     </row>
     <row r="453">
@@ -5987,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>0.135644526591389</v>
+        <v>0.0312789253484763</v>
       </c>
     </row>
     <row r="454">
@@ -6130,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-2.99649502531253</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="467">
@@ -6174,7 +6168,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.152565314877935</v>
       </c>
     </row>
     <row r="471">
@@ -6196,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.246903939901624</v>
+        <v>-0.275434783599673</v>
       </c>
     </row>
     <row r="473">
@@ -6218,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.161724475925451</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="475">
@@ -6229,7 +6223,7 @@
         <v>16</v>
       </c>
       <c r="C475" t="n">
-        <v>-0.315809907561317</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="476">
@@ -6251,7 +6245,7 @@
         <v>16</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.245061106701755</v>
+        <v>-0.33387651119596</v>
       </c>
     </row>
     <row r="478">
@@ -6295,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>0.0757540587999855</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="482">
@@ -6339,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.25398240375319</v>
+        <v>-0.168060714398583</v>
       </c>
     </row>
     <row r="486">
@@ -6350,7 +6344,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.219363829152706</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="487">
@@ -6372,7 +6366,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.155720829509799</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="489">
@@ -6383,7 +6377,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.15921421274642</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="490">
@@ -6394,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.148972113787029</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="491">
@@ -6438,7 +6432,7 @@
         <v>16</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.190520221650631</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="495">
@@ -6471,7 +6465,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.153053018225819</v>
+        <v>-0.150738261861859</v>
       </c>
     </row>
     <row r="498">
@@ -6493,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.556047049121336</v>
+        <v>-0.260691059864452</v>
       </c>
     </row>
     <row r="500">
@@ -6603,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.233188363249031</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="510">
@@ -6625,7 +6619,7 @@
         <v>16</v>
       </c>
       <c r="C511" t="n">
-        <v>-0.191094229801611</v>
+        <v>-0.14866078934246</v>
       </c>
     </row>
     <row r="512">
@@ -6669,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.154745411855252</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="516">
@@ -6746,7 +6740,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.149488768603866</v>
+        <v>-0.149082666278903</v>
       </c>
     </row>
     <row r="523">
@@ -6768,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.277281672827837</v>
+        <v>-0.146908479354949</v>
       </c>
     </row>
     <row r="525">
@@ -6779,7 +6773,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.525664403631718</v>
       </c>
     </row>
     <row r="526">
@@ -6801,7 +6795,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.155776832683384</v>
       </c>
     </row>
     <row r="528">
@@ -6812,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.128744597697945</v>
+        <v>-0.147027940119633</v>
       </c>
     </row>
     <row r="529">
@@ -6845,7 +6839,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.155392594861812</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="532">
@@ -6856,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-1.22462546993059</v>
+        <v>-0.291749408940195</v>
       </c>
     </row>
     <row r="533">
@@ -6900,7 +6894,7 @@
         <v>16</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.236937135152406</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="537">
@@ -6922,7 +6916,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.312632248912752</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="539">
@@ -6944,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.146864252518459</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="541">
@@ -6977,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.230174118162492</v>
       </c>
     </row>
     <row r="544">
@@ -7010,7 +7004,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.196072568279327</v>
+        <v>-0.223625030133678</v>
       </c>
     </row>
     <row r="547">
@@ -7021,7 +7015,7 @@
         <v>16</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.234074497877288</v>
+        <v>-0.347836545402104</v>
       </c>
     </row>
     <row r="548">
@@ -7043,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.418737872704155</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="550">
@@ -7076,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.168440135730385</v>
       </c>
     </row>
     <row r="553">
@@ -7087,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.162410852429886</v>
+        <v>-0.218706897145844</v>
       </c>
     </row>
     <row r="554">
@@ -7098,7 +7092,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.189747898786754</v>
+        <v>-0.22065825674154</v>
       </c>
     </row>
     <row r="555">
@@ -7109,7 +7103,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.32083931812314</v>
+        <v>-0.157767745511744</v>
       </c>
     </row>
     <row r="556">
@@ -7120,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.260279326592044</v>
+        <v>-0.25029528279603</v>
       </c>
     </row>
     <row r="557">
@@ -7131,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.15322336460198</v>
       </c>
     </row>
     <row r="558">
@@ -7153,7 +7147,7 @@
         <v>16</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.135200932490707</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="560">
@@ -7164,7 +7158,7 @@
         <v>16</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.935370261193113</v>
+        <v>-0.39735766509109</v>
       </c>
     </row>
     <row r="561">
@@ -7197,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.744244814074659</v>
       </c>
     </row>
     <row r="564">
@@ -7241,7 +7235,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-0.158793573330589</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="568">
@@ -7274,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.404477231444059</v>
       </c>
     </row>
     <row r="571">
@@ -7296,7 +7290,7 @@
         <v>16</v>
       </c>
       <c r="C572" t="n">
-        <v>-0.22572506105761</v>
+        <v>-0.201466037944484</v>
       </c>
     </row>
     <row r="573">
@@ -7329,7 +7323,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.150405029508063</v>
+        <v>-0.175229087660355</v>
       </c>
     </row>
     <row r="576">
@@ -7373,7 +7367,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.19750506216007</v>
       </c>
     </row>
     <row r="580">
@@ -7384,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.344738624700755</v>
+        <v>-0.266967645078906</v>
       </c>
     </row>
     <row r="581">
@@ -7395,7 +7389,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.124037889103378</v>
       </c>
     </row>
     <row r="582">
@@ -7406,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>0.157790651645683</v>
+        <v>-0.165584822672076</v>
       </c>
     </row>
     <row r="583">
@@ -7417,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.170784946889887</v>
+        <v>-0.171109943056944</v>
       </c>
     </row>
     <row r="584">
@@ -7450,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.288914043299501</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="587">
@@ -7483,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.132174853476344</v>
       </c>
     </row>
     <row r="590">
@@ -7494,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.179354242774199</v>
+        <v>-0.25798073923572</v>
       </c>
     </row>
     <row r="591">
@@ -7505,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.127316678714084</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="592">
@@ -7516,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.312047410563852</v>
+        <v>-0.256614836094049</v>
       </c>
     </row>
     <row r="593">
@@ -7538,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.713602358215291</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="595">
@@ -7560,7 +7554,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-1.3804478507035</v>
+        <v>-0.18844567880521</v>
       </c>
     </row>
     <row r="597">
@@ -7571,7 +7565,7 @@
         <v>16</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.243979356395207</v>
       </c>
     </row>
     <row r="598">
@@ -7615,7 +7609,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.194604133134931</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="602">
@@ -7659,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.209707911006897</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="606">
@@ -7670,7 +7664,7 @@
         <v>16</v>
       </c>
       <c r="C606" t="n">
-        <v>-0.65239290229218</v>
+        <v>-0.149317089285191</v>
       </c>
     </row>
     <row r="607">
@@ -7681,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.563950463344166</v>
+        <v>-0.907506140896998</v>
       </c>
     </row>
     <row r="608">
@@ -7703,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.16205190275149</v>
       </c>
     </row>
     <row r="610">
@@ -7714,7 +7708,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.253596151434328</v>
+        <v>-0.226050301594293</v>
       </c>
     </row>
     <row r="611">
@@ -7747,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>0.548218110782756</v>
+        <v>-0.305484410236325</v>
       </c>
     </row>
     <row r="614">
@@ -7780,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>0.0299003834398209</v>
+        <v>-0.279379323853584</v>
       </c>
     </row>
     <row r="617">
@@ -7802,7 +7796,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>0.112737026734805</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="619">
@@ -7813,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>-1.10861224574309</v>
+        <v>-2.11210847895673</v>
       </c>
     </row>
     <row r="620">
@@ -7824,7 +7818,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.124718582518093</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="621">
@@ -7835,7 +7829,7 @@
         <v>16</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.183566503243362</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="622">
@@ -7868,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.162332150967629</v>
+        <v>-0.312939313489617</v>
       </c>
     </row>
     <row r="625">
@@ -7923,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.161277906850179</v>
+        <v>-0.17683407618255</v>
       </c>
     </row>
     <row r="630">
@@ -7956,7 +7950,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.280906556449387</v>
+        <v>-0.255694641491532</v>
       </c>
     </row>
     <row r="633">
@@ -7967,7 +7961,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.20029984004929</v>
       </c>
     </row>
     <row r="634">
@@ -7989,7 +7983,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.141917728260215</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="636">
@@ -8000,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.153106090884668</v>
+        <v>-0.208687855307771</v>
       </c>
     </row>
     <row r="637">
@@ -8033,7 +8027,7 @@
         <v>16</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.175532379061825</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="640">
@@ -8055,7 +8049,7 @@
         <v>16</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.16572793236556</v>
+        <v>-0.211344246488091</v>
       </c>
     </row>
     <row r="642">
@@ -8066,7 +8060,7 @@
         <v>16</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.145929856168742</v>
       </c>
     </row>
     <row r="643">
@@ -8077,7 +8071,7 @@
         <v>16</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.234101968401266</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="644">
@@ -8088,7 +8082,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.511390122010493</v>
       </c>
     </row>
     <row r="645">
@@ -8099,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.233122030346426</v>
+        <v>-0.238387784423612</v>
       </c>
     </row>
     <row r="646">
@@ -8110,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.148883351247355</v>
+        <v>-0.146191268806902</v>
       </c>
     </row>
     <row r="647">
@@ -8121,7 +8115,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.301264639839723</v>
+        <v>-0.221933163921015</v>
       </c>
     </row>
     <row r="648">
@@ -8132,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.22003746289046</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="649">
@@ -8143,7 +8137,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.809823299514518</v>
+        <v>-0.149137325830785</v>
       </c>
     </row>
     <row r="650">
@@ -8165,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.246357307135389</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="652">
@@ -8187,7 +8181,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.17993000542778</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="654">
@@ -8253,7 +8247,7 @@
         <v>16</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.201613798569304</v>
+        <v>-0.223771114304144</v>
       </c>
     </row>
     <row r="660">
@@ -8275,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.207974096310407</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="662">
@@ -8319,7 +8313,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.190737579170311</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="666">
@@ -8396,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.709840297476754</v>
+        <v>-2.19013980077381</v>
       </c>
     </row>
     <row r="673">
@@ -8407,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.180382133042925</v>
+        <v>-0.204573596231423</v>
       </c>
     </row>
     <row r="674">
@@ -8451,7 +8445,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.231732516536764</v>
+        <v>-0.121221903664207</v>
       </c>
     </row>
     <row r="678">
@@ -8462,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.151307080819563</v>
+        <v>-0.123346331109</v>
       </c>
     </row>
     <row r="679">
@@ -8473,7 +8467,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.393000594062014</v>
+        <v>-0.405619143612868</v>
       </c>
     </row>
     <row r="680">
@@ -8484,7 +8478,7 @@
         <v>16</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.178472684593791</v>
+        <v>-0.188899835904194</v>
       </c>
     </row>
     <row r="681">
@@ -8495,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.165410226262706</v>
+        <v>-0.225153603387698</v>
       </c>
     </row>
     <row r="682">
@@ -8528,7 +8522,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.570241607775482</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="685">
@@ -8572,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.307084264467685</v>
+        <v>-0.161142525021215</v>
       </c>
     </row>
     <row r="689">
@@ -8627,7 +8621,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.148616524421093</v>
+        <v>-0.161616474768995</v>
       </c>
     </row>
     <row r="694">
@@ -8660,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.187470790925592</v>
+        <v>-0.155561651782552</v>
       </c>
     </row>
     <row r="697">
@@ -8682,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.437358946510002</v>
       </c>
     </row>
     <row r="699">
@@ -8693,7 +8687,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.975883390486798</v>
+        <v>-0.00601054727737194</v>
       </c>
     </row>
     <row r="700">
@@ -8704,7 +8698,7 @@
         <v>16</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.462247683509285</v>
+        <v>-0.156042145417432</v>
       </c>
     </row>
     <row r="701">
@@ -8737,7 +8731,7 @@
         <v>16</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.148415197717244</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="704">
@@ -8759,7 +8753,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.156754457961259</v>
       </c>
     </row>
     <row r="706">
@@ -8770,7 +8764,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.267070584626779</v>
+        <v>-0.305200466244488</v>
       </c>
     </row>
     <row r="707">
@@ -8781,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.091111917098105</v>
+        <v>-0.210375867259541</v>
       </c>
     </row>
     <row r="708">
@@ -8792,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.154123939624855</v>
       </c>
     </row>
     <row r="709">
@@ -8814,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.175729763242515</v>
+        <v>-0.17763459459635</v>
       </c>
     </row>
     <row r="711">
@@ -8825,7 +8819,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.762842717628724</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="712">
@@ -8858,7 +8852,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.137792491638823</v>
+        <v>-0.137043640758304</v>
       </c>
     </row>
     <row r="715">
@@ -8880,7 +8874,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.179527342871579</v>
+        <v>-0.199828577877443</v>
       </c>
     </row>
     <row r="717">
@@ -8935,7 +8929,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.170337436498853</v>
+        <v>-0.159144786822366</v>
       </c>
     </row>
     <row r="722">
@@ -8946,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.273102529453211</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="723">
@@ -8957,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.167852486943055</v>
+        <v>-0.159382791681243</v>
       </c>
     </row>
     <row r="724">
@@ -8990,7 +8984,7 @@
         <v>16</v>
       </c>
       <c r="C726" t="n">
-        <v>-0.402974142287381</v>
+        <v>-0.80812435740753</v>
       </c>
     </row>
     <row r="727">
@@ -9023,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.139089941386565</v>
       </c>
     </row>
     <row r="730">
@@ -9111,7 +9105,7 @@
         <v>16</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.57475769245704</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="738">
@@ -9122,7 +9116,7 @@
         <v>16</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.29766989754203</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="739">
@@ -9133,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="C739" t="n">
-        <v>0.00166688391524206</v>
+        <v>-0.106135928156331</v>
       </c>
     </row>
     <row r="740">
@@ -9144,7 +9138,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.267700875651523</v>
+        <v>-0.269859669376787</v>
       </c>
     </row>
     <row r="741">
@@ -9155,7 +9149,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.155237303175656</v>
+        <v>-0.158514867816671</v>
       </c>
     </row>
     <row r="742">
@@ -9166,7 +9160,7 @@
         <v>16</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.162823425867967</v>
+        <v>-0.15134124307661</v>
       </c>
     </row>
     <row r="743">
@@ -9177,7 +9171,7 @@
         <v>16</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.298378694081181</v>
+        <v>-0.240625508942537</v>
       </c>
     </row>
     <row r="744">
@@ -9265,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.153054699521355</v>
+        <v>-0.150430644283056</v>
       </c>
     </row>
     <row r="752">
@@ -9309,7 +9303,7 @@
         <v>16</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.250207331792281</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="756">
@@ -9342,7 +9336,7 @@
         <v>16</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.137052986881149</v>
+        <v>-0.142654363139447</v>
       </c>
     </row>
     <row r="759">
@@ -9364,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.148601854958421</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="761">
@@ -9375,7 +9369,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.116902417819952</v>
+        <v>-0.0507870100797061</v>
       </c>
     </row>
     <row r="762">
@@ -9386,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.159267403046785</v>
+        <v>-0.176660388627981</v>
       </c>
     </row>
     <row r="763">
@@ -9397,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.436127236488701</v>
+        <v>-0.213916705118372</v>
       </c>
     </row>
     <row r="764">
@@ -9419,7 +9413,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.347808552092918</v>
+        <v>-0.466495410124783</v>
       </c>
     </row>
     <row r="766">
@@ -9430,7 +9424,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.547942079128936</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="767">
@@ -9474,7 +9468,7 @@
         <v>16</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.20152585934111</v>
+        <v>-0.181542547075963</v>
       </c>
     </row>
     <row r="771">
@@ -9540,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.187414161412174</v>
+        <v>-0.150295432954983</v>
       </c>
     </row>
     <row r="777">
@@ -9551,7 +9545,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.190311293680148</v>
+        <v>-0.177883269378247</v>
       </c>
     </row>
     <row r="778">
@@ -9584,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.338989047869361</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="781">
@@ -9617,7 +9611,7 @@
         <v>16</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.110576778262619</v>
+        <v>-0.154690649373193</v>
       </c>
     </row>
     <row r="784">
@@ -9628,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.200082582605218</v>
+        <v>-0.149990634511743</v>
       </c>
     </row>
     <row r="785">
@@ -9650,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.149843825250677</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="787">
@@ -9705,7 +9699,7 @@
         <v>16</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.167585870562537</v>
       </c>
     </row>
     <row r="792">
@@ -9727,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.0488004116881864</v>
+        <v>-0.154298652003816</v>
       </c>
     </row>
     <row r="794">
@@ -9738,7 +9732,7 @@
         <v>16</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.207701139445467</v>
+        <v>-0.253464121583263</v>
       </c>
     </row>
     <row r="795">
@@ -9749,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.0782787126371036</v>
+        <v>-0.105224705240412</v>
       </c>
     </row>
     <row r="796">
@@ -9760,7 +9754,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.223788165548456</v>
+        <v>-0.156622981448784</v>
       </c>
     </row>
     <row r="797">
@@ -9771,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.187452846535532</v>
+        <v>-0.193749233849791</v>
       </c>
     </row>
     <row r="798">
@@ -9782,7 +9776,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.226538095799367</v>
+        <v>-0.207415640704668</v>
       </c>
     </row>
     <row r="799">
@@ -9793,7 +9787,7 @@
         <v>16</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.28984968563146</v>
+        <v>-0.516717279400681</v>
       </c>
     </row>
     <row r="800">
@@ -9826,7 +9820,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.210155939389824</v>
+        <v>-0.210326611453974</v>
       </c>
     </row>
     <row r="803">
@@ -9837,7 +9831,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.188473390073821</v>
+        <v>-0.181714175450173</v>
       </c>
     </row>
     <row r="804">
@@ -9848,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.199453689419925</v>
+        <v>-0.331897775520301</v>
       </c>
     </row>
     <row r="805">
@@ -9859,7 +9853,7 @@
         <v>16</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.21485295553849</v>
+        <v>-0.166931081373789</v>
       </c>
     </row>
     <row r="806">
@@ -9870,7 +9864,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.164659429983854</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="807">
@@ -9892,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.179883734444254</v>
+        <v>-0.208002417142819</v>
       </c>
     </row>
     <row r="809">
@@ -9903,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.182201442911816</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="810">
@@ -9936,7 +9930,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.400064804520182</v>
       </c>
     </row>
     <row r="813">
@@ -9947,7 +9941,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.176792167781887</v>
+        <v>-0.151324095772053</v>
       </c>
     </row>
     <row r="814">
@@ -9958,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.263877433846671</v>
+        <v>-0.356693367592663</v>
       </c>
     </row>
     <row r="815">
@@ -9969,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.231704761427994</v>
+        <v>-0.186057324021935</v>
       </c>
     </row>
     <row r="816">
@@ -9980,7 +9974,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.17844603622738</v>
+        <v>-0.191155701159868</v>
       </c>
     </row>
     <row r="817">
@@ -10035,7 +10029,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.387550235329624</v>
+        <v>-0.154921727234737</v>
       </c>
     </row>
     <row r="822">
@@ -10068,7 +10062,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.274166842883207</v>
+        <v>-0.193405866928099</v>
       </c>
     </row>
     <row r="825">
@@ -10090,7 +10084,7 @@
         <v>16</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.119489689959082</v>
+        <v>-0.0577371757137082</v>
       </c>
     </row>
     <row r="827">
@@ -10123,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.166479163359704</v>
+        <v>-0.124957260988993</v>
       </c>
     </row>
     <row r="830">
@@ -10167,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.204971074640438</v>
+        <v>-0.186734372774697</v>
       </c>
     </row>
     <row r="834">
@@ -10178,7 +10172,7 @@
         <v>16</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.168616656367721</v>
+        <v>-0.190656865631566</v>
       </c>
     </row>
     <row r="835">
@@ -10189,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.273608490157544</v>
+        <v>-0.233524619868843</v>
       </c>
     </row>
     <row r="836">
@@ -10211,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.149231430297059</v>
+        <v>-0.157480792676124</v>
       </c>
     </row>
     <row r="838">
@@ -10222,7 +10216,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.208053845591664</v>
       </c>
     </row>
     <row r="839">
@@ -10233,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.149541740552373</v>
       </c>
     </row>
     <row r="840">
@@ -10244,7 +10238,7 @@
         <v>16</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.219854031770336</v>
+        <v>-0.169315101630089</v>
       </c>
     </row>
     <row r="841">
@@ -10266,7 +10260,7 @@
         <v>16</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.222077983570564</v>
+        <v>-0.240459115531271</v>
       </c>
     </row>
     <row r="843">
@@ -10277,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.986961552033546</v>
+        <v>-0.158672880440741</v>
       </c>
     </row>
     <row r="844">
@@ -10288,7 +10282,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.19620008150005</v>
+        <v>-0.16282008530691</v>
       </c>
     </row>
     <row r="845">
@@ -10299,7 +10293,7 @@
         <v>16</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.207932426412173</v>
+        <v>-0.172221783542435</v>
       </c>
     </row>
     <row r="846">
@@ -10332,7 +10326,7 @@
         <v>16</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.147055007977406</v>
+        <v>-0.160947546439417</v>
       </c>
     </row>
     <row r="849">
@@ -10354,7 +10348,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.24076894763598</v>
+        <v>-0.278705720514723</v>
       </c>
     </row>
     <row r="851">
@@ -10365,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.194200408145091</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="852">
@@ -10376,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.267668463237384</v>
+        <v>-1.6412462735917</v>
       </c>
     </row>
     <row r="853">
@@ -10387,7 +10381,7 @@
         <v>16</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.153921093279161</v>
+        <v>-0.157037071815247</v>
       </c>
     </row>
     <row r="854">
@@ -10420,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.14938555202594</v>
+        <v>-0.149085405335193</v>
       </c>
     </row>
     <row r="857">
@@ -10431,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.227578241507267</v>
       </c>
     </row>
     <row r="858">
@@ -10464,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.238238413200482</v>
+        <v>-0.204136395364713</v>
       </c>
     </row>
     <row r="861">
@@ -10519,7 +10513,7 @@
         <v>16</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.211169878390567</v>
+        <v>-0.232236100374945</v>
       </c>
     </row>
     <row r="866">
@@ -10530,7 +10524,7 @@
         <v>16</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.305619149572995</v>
+        <v>-0.16556463806453</v>
       </c>
     </row>
     <row r="867">
@@ -10541,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.403920178112072</v>
+        <v>-0.201227306676113</v>
       </c>
     </row>
     <row r="868">
@@ -10574,7 +10568,7 @@
         <v>16</v>
       </c>
       <c r="C870" t="n">
-        <v>0.0720547275652631</v>
+        <v>-0.189193111951506</v>
       </c>
     </row>
     <row r="871">
@@ -10585,7 +10579,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.162262863588863</v>
+        <v>-0.219616586591537</v>
       </c>
     </row>
     <row r="872">
@@ -10618,7 +10612,7 @@
         <v>16</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.284316379257631</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="875">
@@ -10629,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.374994334814472</v>
+        <v>-0.760091004035156</v>
       </c>
     </row>
     <row r="876">
@@ -10640,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.153688919863425</v>
       </c>
     </row>
     <row r="877">
@@ -10651,7 +10645,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.288882844654213</v>
       </c>
     </row>
     <row r="878">
@@ -10684,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.152110843479449</v>
+        <v>-0.166219868289531</v>
       </c>
     </row>
     <row r="881">
@@ -10695,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.232824321925398</v>
+        <v>-0.475108512064811</v>
       </c>
     </row>
     <row r="882">
@@ -10706,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.246997858147602</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="883">
@@ -10717,7 +10711,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.217775776347557</v>
+        <v>-0.0543547186499045</v>
       </c>
     </row>
     <row r="884">
@@ -10728,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.237432631433977</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="885">
@@ -10739,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.234210609514771</v>
       </c>
     </row>
     <row r="886">
@@ -10750,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.19725760718004</v>
+        <v>-0.224800261041976</v>
       </c>
     </row>
     <row r="887">
@@ -10761,7 +10755,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.481343074553644</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="888">
@@ -10783,7 +10777,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.371735617550635</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="890">
@@ -10805,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.402162573307991</v>
+        <v>-0.514474154525851</v>
       </c>
     </row>
     <row r="892">
@@ -10816,7 +10810,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.206117160544461</v>
+        <v>-0.415415049408792</v>
       </c>
     </row>
     <row r="893">
@@ -10849,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.149515970922093</v>
       </c>
     </row>
     <row r="896">
@@ -10860,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.178063418507551</v>
+        <v>-0.165052799876044</v>
       </c>
     </row>
     <row r="897">
@@ -10871,7 +10865,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.380899011688923</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="898">
@@ -10915,7 +10909,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.152787491370638</v>
+        <v>-0.464374497730811</v>
       </c>
     </row>
     <row r="902">
@@ -10926,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.153926828183559</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="903">
@@ -10948,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.176952046706641</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="905">
@@ -10959,7 +10953,7 @@
         <v>16</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.233638954676113</v>
+        <v>-0.214171864167806</v>
       </c>
     </row>
     <row r="906">
@@ -10981,7 +10975,7 @@
         <v>16</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.158646150064952</v>
+        <v>-0.155500009075699</v>
       </c>
     </row>
     <row r="908">
@@ -11003,7 +10997,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.461642998886763</v>
+        <v>-0.104904074058481</v>
       </c>
     </row>
     <row r="910">
@@ -11080,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.151927903712024</v>
+        <v>-0.173226724902995</v>
       </c>
     </row>
     <row r="917">
@@ -11091,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.328043877901293</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="918">
@@ -11102,7 +11096,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.194443284478661</v>
+        <v>-0.201684419111821</v>
       </c>
     </row>
     <row r="919">
@@ -11124,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.168040330151986</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="921">
@@ -11157,7 +11151,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.297441560480476</v>
+        <v>-0.175467371773176</v>
       </c>
     </row>
     <row r="924">
@@ -11190,7 +11184,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.171488870317754</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="927">
@@ -11201,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.169364007188484</v>
+        <v>-0.147998415887423</v>
       </c>
     </row>
     <row r="928">
@@ -11223,7 +11217,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.263499876690143</v>
+        <v>-0.143381256364872</v>
       </c>
     </row>
     <row r="930">
@@ -11267,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.24168089744551</v>
+        <v>-0.266694277617396</v>
       </c>
     </row>
     <row r="934">
@@ -11278,7 +11272,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.312603249277765</v>
+        <v>-0.155556533447202</v>
       </c>
     </row>
     <row r="935">
@@ -11289,7 +11283,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.165497479200993</v>
+        <v>0.243783612113906</v>
       </c>
     </row>
     <row r="936">
@@ -11311,7 +11305,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.140651939710035</v>
       </c>
     </row>
     <row r="938">
@@ -11344,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.110890051562679</v>
+        <v>-0.169270099019325</v>
       </c>
     </row>
     <row r="941">
@@ -11366,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.250166744191245</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="943">
@@ -11377,7 +11371,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.470970028363957</v>
+        <v>-0.215712360941556</v>
       </c>
     </row>
     <row r="944">
@@ -11410,7 +11404,7 @@
         <v>16</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.148693624955479</v>
+        <v>-0.350805624985701</v>
       </c>
     </row>
     <row r="947">
@@ -11421,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.215333987029692</v>
+        <v>-0.215094167899653</v>
       </c>
     </row>
     <row r="948">
@@ -11432,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.200770717750556</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="949">
@@ -11487,7 +11481,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.217527298469666</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="954">
@@ -11509,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.167825083259831</v>
       </c>
     </row>
     <row r="956">
@@ -11520,7 +11514,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.256319643454659</v>
+        <v>-0.222697774762135</v>
       </c>
     </row>
     <row r="957">
@@ -11531,7 +11525,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.152668156885899</v>
       </c>
     </row>
     <row r="958">
@@ -11597,7 +11591,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.470294510608969</v>
+        <v>-0.296999022456092</v>
       </c>
     </row>
     <row r="964">
@@ -11608,7 +11602,7 @@
         <v>16</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.162305422795916</v>
       </c>
     </row>
     <row r="965">
@@ -11619,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.156338362003761</v>
+        <v>-0.15063646721874</v>
       </c>
     </row>
     <row r="966">
@@ -11630,7 +11624,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.24746978131118</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="967">
@@ -11641,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.155720764020177</v>
       </c>
     </row>
     <row r="968">
@@ -11663,7 +11657,7 @@
         <v>16</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.246348616605048</v>
       </c>
     </row>
     <row r="970">
@@ -11707,7 +11701,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>0.20515211282571</v>
+        <v>-0.249556788521852</v>
       </c>
     </row>
     <row r="974">
@@ -11729,7 +11723,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.17902748761667</v>
+        <v>-0.162210777159979</v>
       </c>
     </row>
     <row r="976">
@@ -11751,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.243373706481111</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="978">
@@ -11762,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.25202348832478</v>
+        <v>-0.322835681403127</v>
       </c>
     </row>
     <row r="979">
@@ -11773,7 +11767,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.107404972286774</v>
+        <v>0.0656001678222331</v>
       </c>
     </row>
     <row r="980">
@@ -11817,7 +11811,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.275294994068529</v>
+        <v>-0.31191405326161</v>
       </c>
     </row>
     <row r="984">
@@ -11839,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.227318484281277</v>
+        <v>-0.212821447710935</v>
       </c>
     </row>
     <row r="986">
@@ -11927,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.270476037028613</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="994">
@@ -11982,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.129400854756231</v>
+        <v>-0.0425654608086343</v>
       </c>
     </row>
     <row r="999">
@@ -12004,7 +11998,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.122416753121428</v>
+        <v>-0.0964150749334283</v>
       </c>
     </row>
     <row r="1001">
@@ -12015,7 +12009,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.26305809831651</v>
+        <v>-0.257145010429662</v>
       </c>
     </row>
     <row r="1002">
@@ -12048,7 +12042,7 @@
         <v>16</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.505661652853896</v>
       </c>
     </row>
     <row r="1005">
@@ -12059,7 +12053,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.160374579632151</v>
+        <v>-0.0473355359125474</v>
       </c>
     </row>
     <row r="1006">
@@ -12070,7 +12064,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.176397155645597</v>
       </c>
     </row>
     <row r="1007">
@@ -12092,7 +12086,7 @@
         <v>16</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.178156562483184</v>
       </c>
     </row>
     <row r="1009">
@@ -12103,7 +12097,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.307390499282218</v>
       </c>
     </row>
     <row r="1010">
@@ -12114,7 +12108,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.170418081314282</v>
+        <v>-0.22148401935762</v>
       </c>
     </row>
     <row r="1011">
@@ -12136,7 +12130,7 @@
         <v>16</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.269737052820063</v>
       </c>
     </row>
     <row r="1013">
@@ -12147,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.160465317807424</v>
+        <v>-0.163977821306278</v>
       </c>
     </row>
     <row r="1014">
@@ -12169,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.165693646246985</v>
       </c>
     </row>
     <row r="1016">
@@ -12180,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.15901871948252</v>
+        <v>-0.169661095925415</v>
       </c>
     </row>
     <row r="1017">
@@ -12213,7 +12207,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>-0.156655601527406</v>
+        <v>-0.161559089708977</v>
       </c>
     </row>
     <row r="1020">
@@ -12246,7 +12240,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.696429526475627</v>
       </c>
     </row>
     <row r="1023">
@@ -12257,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.164357996623053</v>
       </c>
     </row>
     <row r="1024">
@@ -12323,7 +12317,7 @@
         <v>16</v>
       </c>
       <c r="C1029" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.26700928548184</v>
       </c>
     </row>
     <row r="1030">
@@ -12334,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.043715065385374</v>
       </c>
     </row>
     <row r="1031">
@@ -12345,7 +12339,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.041291982046809</v>
       </c>
     </row>
     <row r="1032">
@@ -12367,7 +12361,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.16073008286798</v>
+        <v>-0.17747897386085</v>
       </c>
     </row>
     <row r="1034">
@@ -12378,7 +12372,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.553039644115122</v>
       </c>
     </row>
     <row r="1035">
@@ -12411,7 +12405,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.108687546970456</v>
+        <v>0.254530510634428</v>
       </c>
     </row>
     <row r="1038">
@@ -12444,7 +12438,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.166451882578001</v>
       </c>
     </row>
     <row r="1041">
@@ -12532,7 +12526,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.449700953311484</v>
       </c>
     </row>
     <row r="1049">
@@ -12554,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.21354757200133</v>
       </c>
     </row>
     <row r="1051">
@@ -12565,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.165549437736427</v>
       </c>
     </row>
     <row r="1052">
@@ -12598,7 +12592,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.161030242652552</v>
+        <v>-0.197075915074452</v>
       </c>
     </row>
     <row r="1055">
@@ -12609,7 +12603,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.171803159197053</v>
       </c>
     </row>
     <row r="1056">
@@ -12664,7 +12658,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.076002207170003</v>
       </c>
     </row>
     <row r="1061">
@@ -12686,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.503538151588006</v>
       </c>
     </row>
     <row r="1063">
@@ -12730,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.147349686476303</v>
+        <v>-2.02137327922362</v>
       </c>
     </row>
     <row r="1067">
@@ -12752,7 +12746,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.288491605412083</v>
       </c>
     </row>
     <row r="1069">
@@ -12763,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.167351854000171</v>
       </c>
     </row>
     <row r="1070">
@@ -12774,7 +12768,7 @@
         <v>16</v>
       </c>
       <c r="C1070" t="n">
-        <v>-0.165094948283982</v>
+        <v>0.0893900721323652</v>
       </c>
     </row>
     <row r="1071">
@@ -12829,7 +12823,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.187540122736685</v>
       </c>
     </row>
     <row r="1076">
@@ -12840,7 +12834,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.161574371204938</v>
       </c>
     </row>
     <row r="1077">
@@ -12884,7 +12878,7 @@
         <v>16</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.227944544612028</v>
       </c>
     </row>
     <row r="1081">
@@ -12895,7 +12889,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.136494002293503</v>
+        <v>-0.112813398571738</v>
       </c>
     </row>
     <row r="1082">
@@ -12928,7 +12922,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.184040558810385</v>
       </c>
     </row>
     <row r="1085">
@@ -12939,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.162773144088758</v>
       </c>
     </row>
     <row r="1086">
@@ -12983,7 +12977,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>-0.16658278353481</v>
+        <v>-0.308036530285018</v>
       </c>
     </row>
     <row r="1090">
@@ -13005,7 +12999,7 @@
         <v>16</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.16143829528295</v>
+        <v>0.0277924139496704</v>
       </c>
     </row>
     <row r="1092">
@@ -13016,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.169838480361731</v>
       </c>
     </row>
     <row r="1093">
@@ -13027,7 +13021,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.167975593659276</v>
       </c>
     </row>
     <row r="1094">
@@ -13038,7 +13032,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.152947926021333</v>
+        <v>0.225992833306913</v>
       </c>
     </row>
     <row r="1095">
@@ -13060,7 +13054,7 @@
         <v>16</v>
       </c>
       <c r="C1096" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.344415570278334</v>
       </c>
     </row>
     <row r="1097">
@@ -13148,7 +13142,7 @@
         <v>16</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.15899744566479</v>
+        <v>-0.0554038421163621</v>
       </c>
     </row>
     <row r="1105">
@@ -13170,7 +13164,7 @@
         <v>16</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.088698266497534</v>
       </c>
     </row>
     <row r="1107">
@@ -13247,7 +13241,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.300835733107546</v>
       </c>
     </row>
     <row r="1114">
@@ -13258,7 +13252,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.165985325611782</v>
       </c>
     </row>
     <row r="1115">
@@ -13269,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.33963247673032</v>
       </c>
     </row>
     <row r="1116">
@@ -13313,7 +13307,7 @@
         <v>16</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0269480137182285</v>
       </c>
     </row>
     <row r="1120">
@@ -13324,7 +13318,7 @@
         <v>16</v>
       </c>
       <c r="C1120" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.107070804793953</v>
       </c>
     </row>
     <row r="1121">
@@ -13335,7 +13329,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.159922072645701</v>
+        <v>-0.132639770639691</v>
       </c>
     </row>
     <row r="1122">
@@ -13379,7 +13373,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>-0.163909084873574</v>
+        <v>-0.20137228626438</v>
       </c>
     </row>
     <row r="1126">
@@ -13500,7 +13494,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.186702858443373</v>
       </c>
     </row>
     <row r="1137">
@@ -13533,7 +13527,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.1604828783346</v>
+        <v>-0.200869148401914</v>
       </c>
     </row>
     <row r="1140">
@@ -13588,7 +13582,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.21657752688294</v>
       </c>
     </row>
     <row r="1145">
@@ -13720,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.173780678959589</v>
       </c>
     </row>
     <row r="1157">
@@ -13742,7 +13736,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.548402195172093</v>
       </c>
     </row>
     <row r="1159">
@@ -13797,7 +13791,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.226210392396808</v>
       </c>
     </row>
     <row r="1164">
@@ -13874,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.159763313609467</v>
+        <v>-5.61627141189492</v>
       </c>
     </row>
     <row r="1171">
@@ -13885,7 +13879,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.390888418558012</v>
       </c>
     </row>
     <row r="1172">
@@ -13907,7 +13901,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.256172443602076</v>
       </c>
     </row>
     <row r="1174">
@@ -13929,7 +13923,7 @@
         <v>16</v>
       </c>
       <c r="C1175" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.0139499348864225</v>
       </c>
     </row>
     <row r="1176">
@@ -13995,7 +13989,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.198915064767544</v>
       </c>
     </row>
     <row r="1182">
@@ -14028,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.173829391866766</v>
       </c>
     </row>
     <row r="1185">
@@ -14050,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.137060454697394</v>
       </c>
     </row>
     <row r="1187">
@@ -14061,7 +14055,7 @@
         <v>16</v>
       </c>
       <c r="C1187" t="n">
-        <v>-0.160630810084253</v>
+        <v>-0.180711940028915</v>
       </c>
     </row>
     <row r="1188">
@@ -14083,7 +14077,7 @@
         <v>16</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.22042633920976</v>
       </c>
     </row>
     <row r="1190">
@@ -14094,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.190147853338134</v>
+        <v>-0.988441022926744</v>
       </c>
     </row>
     <row r="1191">
@@ -14127,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.56650404358403</v>
       </c>
     </row>
     <row r="1194">
@@ -14138,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.176860034360509</v>
       </c>
     </row>
     <row r="1195">
@@ -14160,7 +14154,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.26324773602358</v>
       </c>
     </row>
     <row r="1197">
@@ -14171,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.29554715593188</v>
       </c>
     </row>
     <row r="1198">
@@ -14182,7 +14176,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.118623974839006</v>
       </c>
     </row>
     <row r="1199">
@@ -14193,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.176108582934313</v>
       </c>
     </row>
     <row r="1200">
@@ -14294,7 +14288,7 @@
         <v>13.69</v>
       </c>
       <c r="E4" t="n">
-        <v>4.23357142857143</v>
+        <v>3.68428124385062</v>
       </c>
     </row>
     <row r="5">
@@ -14328,7 +14322,7 @@
         <v>14.93</v>
       </c>
       <c r="E6" t="n">
-        <v>18.3912045783071</v>
+        <v>22.155861200807</v>
       </c>
     </row>
     <row r="7">
@@ -14362,7 +14356,7 @@
         <v>8.06</v>
       </c>
       <c r="E8" t="n">
-        <v>3.96429341065403</v>
+        <v>3.1701256508595</v>
       </c>
     </row>
     <row r="9">
@@ -14379,7 +14373,7 @@
         <v>0.79</v>
       </c>
       <c r="E9" t="n">
-        <v>5.13614235406013</v>
+        <v>4.98188550342905</v>
       </c>
     </row>
     <row r="10">
@@ -14396,7 +14390,7 @@
         <v>0.85</v>
       </c>
       <c r="E10" t="n">
-        <v>5.15071428571428</v>
+        <v>4.70122069459807</v>
       </c>
     </row>
     <row r="11">
@@ -14430,7 +14424,7 @@
         <v>-0.74</v>
       </c>
       <c r="E12" t="n">
-        <v>5.26428571428571</v>
+        <v>4.9210503407581</v>
       </c>
     </row>
     <row r="13">
@@ -14447,7 +14441,7 @@
         <v>-1.86</v>
       </c>
       <c r="E13" t="n">
-        <v>6.49152415152826</v>
+        <v>6.88700395747698</v>
       </c>
     </row>
     <row r="14">
@@ -14464,7 +14458,7 @@
         <v>-6.6</v>
       </c>
       <c r="E14" t="n">
-        <v>5.54289226544007</v>
+        <v>5.2268703228183</v>
       </c>
     </row>
     <row r="15">
@@ -14498,7 +14492,7 @@
         <v>-0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>5.24571428571428</v>
+        <v>5.22184775239695</v>
       </c>
     </row>
     <row r="17">
@@ -14702,7 +14696,7 @@
         <v>-2646.36</v>
       </c>
       <c r="E28" t="n">
-        <v>-21.9785714285714</v>
+        <v>39.1166069374045</v>
       </c>
     </row>
     <row r="29">
@@ -15093,7 +15087,7 @@
         <v>2.983</v>
       </c>
       <c r="E51" t="n">
-        <v>2.18034249664147</v>
+        <v>2.29904096690387</v>
       </c>
     </row>
     <row r="52">
@@ -15127,7 +15121,7 @@
         <v>3.879</v>
       </c>
       <c r="E53" t="n">
-        <v>1.67582834195095</v>
+        <v>1.68756692961322</v>
       </c>
     </row>
     <row r="54">
@@ -15229,7 +15223,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>2.1949609578961</v>
+        <v>2.10257142857143</v>
       </c>
     </row>
     <row r="60">
@@ -15976,13 +15970,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>15</v>
@@ -15993,13 +15987,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>15</v>
@@ -16016,7 +16010,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>15</v>
@@ -16033,7 +16027,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -16050,7 +16044,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
         <v>15</v>
@@ -16067,7 +16061,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
         <v>15</v>
@@ -16084,7 +16078,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -16101,7 +16095,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -16118,7 +16112,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" t="n">
         <v>15</v>
@@ -16135,7 +16129,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" t="n">
         <v>15</v>
@@ -16152,7 +16146,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D23" t="n">
         <v>15</v>
@@ -16163,13 +16157,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D24" t="n">
         <v>15</v>
@@ -16180,13 +16174,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D25" t="n">
         <v>15</v>
@@ -16197,13 +16191,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D26" t="n">
         <v>15</v>
@@ -16214,13 +16208,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D27" t="n">
         <v>15</v>
@@ -16237,7 +16231,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D28" t="n">
         <v>15</v>
@@ -16254,7 +16248,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D29" t="n">
         <v>15</v>
@@ -16271,7 +16265,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D30" t="n">
         <v>15</v>
@@ -16288,7 +16282,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D31" t="n">
         <v>15</v>
@@ -16305,7 +16299,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D32" t="n">
         <v>15</v>
@@ -16322,7 +16316,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D33" t="n">
         <v>15</v>
@@ -16339,7 +16333,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D34" t="n">
         <v>15</v>
@@ -16350,13 +16344,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D35" t="n">
         <v>15</v>
@@ -16367,13 +16361,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D36" t="n">
         <v>15</v>
@@ -16384,13 +16378,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D37" t="n">
         <v>15</v>
@@ -16401,13 +16395,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D38" t="n">
         <v>15</v>
@@ -16418,13 +16412,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D39" t="n">
         <v>15</v>
@@ -16435,13 +16429,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D40" t="n">
         <v>15</v>
@@ -16458,7 +16452,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D41" t="n">
         <v>15</v>
@@ -16475,7 +16469,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
         <v>15</v>
@@ -16492,7 +16486,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D43" t="n">
         <v>15</v>
@@ -16509,7 +16503,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D44" t="n">
         <v>15</v>
@@ -16526,7 +16520,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D45" t="n">
         <v>15</v>
@@ -16537,13 +16531,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D46" t="n">
         <v>15</v>
@@ -16554,13 +16548,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D47" t="n">
         <v>15</v>
@@ -16571,13 +16565,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D48" t="n">
         <v>15</v>
@@ -16588,13 +16582,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D49" t="n">
         <v>15</v>
@@ -16605,13 +16599,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D50" t="n">
         <v>15</v>
@@ -16622,13 +16616,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D51" t="n">
         <v>15</v>
@@ -16639,13 +16633,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D52" t="n">
         <v>15</v>
@@ -16656,13 +16650,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D53" t="n">
         <v>15</v>
@@ -16679,7 +16673,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D54" t="n">
         <v>15</v>
@@ -16696,7 +16690,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D55" t="n">
         <v>15</v>
@@ -16713,7 +16707,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D56" t="n">
         <v>15</v>
@@ -16724,16 +16718,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
         <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -16741,16 +16735,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -16758,16 +16752,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
         <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -16775,16 +16769,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -16792,16 +16786,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
         <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -16809,16 +16803,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
         <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -16826,16 +16820,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
         <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -16843,16 +16837,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
         <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -16860,16 +16854,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
         <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D65" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -16877,16 +16871,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
         <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D66" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -16900,216 +16894,12 @@
         <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D67" t="n">
         <v>14</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" t="n">
-        <v>14</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="s">
-        <v>45</v>
-      </c>
-      <c r="D69" t="n">
-        <v>14</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>21</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="s">
-        <v>46</v>
-      </c>
-      <c r="D70" t="n">
-        <v>14</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="s">
-        <v>47</v>
-      </c>
-      <c r="D71" t="n">
-        <v>14</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>21</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>48</v>
-      </c>
-      <c r="D72" t="n">
-        <v>14</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="s">
-        <v>49</v>
-      </c>
-      <c r="D73" t="n">
-        <v>14</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="s">
-        <v>50</v>
-      </c>
-      <c r="D74" t="n">
-        <v>14</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>21</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="s">
-        <v>51</v>
-      </c>
-      <c r="D75" t="n">
-        <v>14</v>
-      </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="s">
-        <v>52</v>
-      </c>
-      <c r="D76" t="n">
-        <v>14</v>
-      </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>21</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="s">
-        <v>53</v>
-      </c>
-      <c r="D77" t="n">
-        <v>14</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="s">
-        <v>54</v>
-      </c>
-      <c r="D78" t="n">
-        <v>14</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>21</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="s">
-        <v>55</v>
-      </c>
-      <c r="D79" t="n">
-        <v>14</v>
-      </c>
-      <c r="E79" t="n">
         <v>1</v>
       </c>
     </row>
